--- a/shared_uploads/fillrate.xlsx
+++ b/shared_uploads/fillrate.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\C960806\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDA16E1F-3ABB-4467-9BCB-D3313E3DED20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{519DE793-BC26-4029-8291-AA19EC646168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="329">
   <si>
     <t>TOTAL</t>
   </si>
@@ -33,915 +33,174 @@
     <t>Bahía Blanca ▾</t>
   </si>
   <si>
-    <t>36.950 ▲ 10.2%vs MA</t>
-  </si>
-  <si>
-    <t>1.553 4.2% ▲ 20.6%vs MA</t>
-  </si>
-  <si>
-    <t>108 0.3% ▼ 21.2%vs MA</t>
-  </si>
-  <si>
-    <t>$5 M ▲ 23.0%vs MA</t>
-  </si>
-  <si>
-    <t>94.6% ▼ 0.1%vs MA</t>
-  </si>
-  <si>
     <t>Constituyentes ▾</t>
   </si>
   <si>
-    <t>111.555 ▲ 24.2%vs MA</t>
-  </si>
-  <si>
-    <t>1.064 1.0% ▼ 25.1%vs MA</t>
-  </si>
-  <si>
-    <t>1.659 1.5% ▼ 8.7%vs MA</t>
-  </si>
-  <si>
-    <t>$4 M ▼ 33.3%vs MA</t>
-  </si>
-  <si>
-    <t>97.9% ▲ 1.2%vs MA</t>
-  </si>
-  <si>
     <t>Avellaneda ▾</t>
   </si>
   <si>
-    <t>64.122 ▲ 22.5%vs MA</t>
-  </si>
-  <si>
-    <t>909 1.4% ▲ 8.7%vs MA</t>
-  </si>
-  <si>
-    <t>1.729 2.7% ▲ 11.8%vs MA</t>
-  </si>
-  <si>
-    <t>$3 M ▲ 26.3%vs MA</t>
-  </si>
-  <si>
-    <t>98.0% ▲ 0.3%vs MA</t>
-  </si>
-  <si>
     <t>Formosa ▾</t>
   </si>
   <si>
-    <t>27.618 ▲ 30.1%vs MA</t>
-  </si>
-  <si>
-    <t>536 1.9% ▼ 13.8%vs MA</t>
-  </si>
-  <si>
-    <t>17 0.1% ▼ 26.1%vs MA</t>
-  </si>
-  <si>
-    <t>$1 M ▼ 19.1%vs MA</t>
-  </si>
-  <si>
-    <t>97.5% ▲ 1.2%vs MA</t>
-  </si>
-  <si>
     <t>Córdoba Oeste ▾</t>
   </si>
   <si>
-    <t>95.172 ▲ 60.0%vs MA</t>
-  </si>
-  <si>
-    <t>436 0.5% ▲ 67.0%vs MA</t>
-  </si>
-  <si>
-    <t>1.115 1.2% ▲ 68.4%vs MA</t>
-  </si>
-  <si>
-    <t>$1 M ▲ 15.8%vs MA</t>
-  </si>
-  <si>
-    <t>98.9% ▲ 0.3%vs MA</t>
-  </si>
-  <si>
     <t>San Justo ▾</t>
   </si>
   <si>
-    <t>76.432 ▲ 31.8%vs MA</t>
-  </si>
-  <si>
-    <t>383 0.5% ▼ 2.8%vs MA</t>
-  </si>
-  <si>
-    <t>717 0.9% ▼ 2.6%vs MA</t>
-  </si>
-  <si>
-    <t>$1 M ▼ 2.3%vs MA</t>
-  </si>
-  <si>
-    <t>98.9% ▲ 0.4%vs MA</t>
-  </si>
-  <si>
     <t>Guaymallén ▾</t>
   </si>
   <si>
-    <t>56.707 ▲ 38.4%vs MA</t>
-  </si>
-  <si>
-    <t>319 0.6% ▼ 35.2%vs MA</t>
-  </si>
-  <si>
-    <t>665 1.2% ▼ 33.2%vs MA</t>
-  </si>
-  <si>
-    <t>$1 M ▼ 36.6%vs MA</t>
-  </si>
-  <si>
-    <t>99.0% ▲ 0.7%vs MA</t>
-  </si>
-  <si>
     <t>Cipolletti ▾</t>
   </si>
   <si>
-    <t>11.056 ▲ 26.4%vs MA</t>
-  </si>
-  <si>
-    <t>393 3.6% ▼ 24.1%vs MA</t>
-  </si>
-  <si>
-    <t>84 0.8% ▲ 40.0%vs MA</t>
-  </si>
-  <si>
-    <t>$1 M ▼ 6.0%vs MA</t>
-  </si>
-  <si>
-    <t>95.4% ▲ 2.9%vs MA</t>
-  </si>
-  <si>
     <t>La Plata ▾</t>
   </si>
   <si>
-    <t>67.022 ▲ 24.7%vs MA</t>
-  </si>
-  <si>
-    <t>284 0.4% ▼ 37.7%vs MA</t>
-  </si>
-  <si>
-    <t>391 0.6% ▼ 5.6%vs MA</t>
-  </si>
-  <si>
-    <t>$924K ▼ 36.6%vs MA</t>
-  </si>
-  <si>
-    <t>98.8% ▲ 0.7%vs MA</t>
-  </si>
-  <si>
     <t>Neuquén ▾</t>
   </si>
   <si>
-    <t>27.787 ▲ 32.8%vs MA</t>
-  </si>
-  <si>
-    <t>211 0.8% ▲ 18.5%vs MA</t>
-  </si>
-  <si>
-    <t>289 1.0% ▲ 41.0%vs MA</t>
-  </si>
-  <si>
-    <t>$920K ▲ 23.1%vs MA</t>
-  </si>
-  <si>
-    <t>98.5% ▲ 0.2%vs MA</t>
-  </si>
-  <si>
     <t>Pilar ▾</t>
   </si>
   <si>
-    <t>29.022 ▲ 44.7%vs MA</t>
-  </si>
-  <si>
-    <t>280 1.0% ▼ 40.9%vs MA</t>
-  </si>
-  <si>
-    <t>183 0.6% ▲ 169.1%vs MA</t>
-  </si>
-  <si>
-    <t>$878K ▼ 47.8%vs MA</t>
-  </si>
-  <si>
-    <t>97.8% ▲ 2.0%vs MA</t>
-  </si>
-  <si>
     <t>Paraná ▾</t>
   </si>
   <si>
-    <t>32.202 ▲ 16.1%vs MA</t>
-  </si>
-  <si>
-    <t>236 0.7% ▼ 45.1%vs MA</t>
-  </si>
-  <si>
-    <t>43 0.1% ▼ 53.3%vs MA</t>
-  </si>
-  <si>
-    <t>$808K ▼ 47.5%vs MA</t>
-  </si>
-  <si>
-    <t>99.1% ▲ 0.9%vs MA</t>
-  </si>
-  <si>
     <t>Comodoro Sur ▾</t>
   </si>
   <si>
-    <t>23.254 ▲ 21.4%vs MA</t>
-  </si>
-  <si>
-    <t>213 0.9% ▼ 20.5%vs MA</t>
-  </si>
-  <si>
-    <t>383 1.6% ▲ 2.1%vs MA</t>
-  </si>
-  <si>
-    <t>$689K ▼ 9.9%vs MA</t>
-  </si>
-  <si>
-    <t>98.1% ▲ 0.6%vs MA</t>
-  </si>
-  <si>
     <t>San Fernando ▾</t>
   </si>
   <si>
-    <t>33.377 ▼ 13.6%vs MA</t>
-  </si>
-  <si>
-    <t>187 0.6% ▼ 25.5%vs MA</t>
-  </si>
-  <si>
-    <t>373 1.1% ▼ 45.6%vs MA</t>
-  </si>
-  <si>
-    <t>$578K ▼ 36.8%vs MA</t>
-  </si>
-  <si>
-    <t>98.5% ▲ 0.1%vs MA</t>
-  </si>
-  <si>
     <t>Tucumán ▾</t>
   </si>
   <si>
-    <t>29.170 ▲ 29.1%vs MA</t>
-  </si>
-  <si>
-    <t>149 0.5% ▼ 57.1%vs MA</t>
-  </si>
-  <si>
-    <t>257 0.9% ▼ 42.1%vs MA</t>
-  </si>
-  <si>
-    <t>$533K ▼ 60.4%vs MA</t>
-  </si>
-  <si>
-    <t>99.1% ▲ 1.3%vs MA</t>
-  </si>
-  <si>
     <t>San Luis ▾</t>
   </si>
   <si>
-    <t>25.164 ▲ 58.3%vs MA</t>
-  </si>
-  <si>
-    <t>197 0.8% ▼ 9.6%vs MA</t>
-  </si>
-  <si>
-    <t>226 0.9% ▲ 0.9%vs MA</t>
-  </si>
-  <si>
-    <t>$503K ▼ 31.4%vs MA</t>
-  </si>
-  <si>
-    <t>98.9% ▲ 0.8%vs MA</t>
-  </si>
-  <si>
     <t>Santa Fé ▾</t>
   </si>
   <si>
-    <t>46.127 ▲ 32.1%vs MA</t>
-  </si>
-  <si>
-    <t>100 0.2% ▼ 54.3%vs MA</t>
-  </si>
-  <si>
-    <t>114 0.2% ▼ 41.8%vs MA</t>
-  </si>
-  <si>
-    <t>$481K ▼ 45.2%vs MA</t>
-  </si>
-  <si>
-    <t>99.1% ▲ 0.7%vs MA</t>
-  </si>
-  <si>
     <t>San Juan ▾</t>
   </si>
   <si>
-    <t>20.552 ▲ 31.9%vs MA</t>
-  </si>
-  <si>
-    <t>160 0.8% ▼ 45.8%vs MA</t>
-  </si>
-  <si>
-    <t>26 0.1% ▲ 52.9%vs MA</t>
-  </si>
-  <si>
-    <t>$434K ▼ 50.3%vs MA</t>
-  </si>
-  <si>
-    <t>99.0% ▲ 1.2%vs MA</t>
-  </si>
-  <si>
     <t>Rio Cuarto ▾</t>
   </si>
   <si>
-    <t>32.698 ▲ 37.0%vs MA</t>
-  </si>
-  <si>
-    <t>160 0.5% ▼ 68.9%vs MA</t>
-  </si>
-  <si>
-    <t>306 0.9% ▼ 49.2%vs MA</t>
-  </si>
-  <si>
-    <t>$417K ▼ 73.0%vs MA</t>
-  </si>
-  <si>
-    <t>99.4% ▲ 2.2%vs MA</t>
-  </si>
-  <si>
     <t>Lujan ▾</t>
   </si>
   <si>
-    <t>5.291 ▼ 26.7%vs MA</t>
-  </si>
-  <si>
-    <t>126 2.4% ▼ 16.0%vs MA</t>
-  </si>
-  <si>
-    <t>16 0.3% ▲ 33.3%vs MA</t>
-  </si>
-  <si>
-    <t>$343K ▼ 48.8%vs MA</t>
-  </si>
-  <si>
-    <t>97.1% ▲ 0.1%vs MA</t>
-  </si>
-  <si>
     <t>Olavarría ▾</t>
   </si>
   <si>
-    <t>15.741 ▲ 12.7%vs MA</t>
-  </si>
-  <si>
-    <t>128 0.8% ▼ 9.2%vs MA</t>
-  </si>
-  <si>
-    <t>54 0.3% ▲ 10.2%vs MA</t>
-  </si>
-  <si>
-    <t>$285K ▼ 12.0%vs MA</t>
-  </si>
-  <si>
-    <t>99.0% ▲ 0.4%vs MA</t>
-  </si>
-  <si>
     <t>Corrientes ▾</t>
   </si>
   <si>
-    <t>14.784 ▲ 39.3%vs MA</t>
-  </si>
-  <si>
-    <t>131 0.9% ▲ 63.7%vs MA</t>
-  </si>
-  <si>
-    <t>100 0.7% ▲ 53.8%vs MA</t>
-  </si>
-  <si>
-    <t>$249K ▲ 46.1%vs MA</t>
-  </si>
-  <si>
     <t>98.7% ▲ 0.0%vs MA</t>
   </si>
   <si>
     <t>Salta ▾</t>
   </si>
   <si>
-    <t>6.761 ▲ 21.2%vs MA</t>
-  </si>
-  <si>
-    <t>133 2.0% ▲ 30.4%vs MA</t>
-  </si>
-  <si>
-    <t>10 0.1% ▼ 23.1%vs MA</t>
-  </si>
-  <si>
-    <t>$243K ▼ 42.0%vs MA</t>
-  </si>
-  <si>
-    <t>98.0% ▲ 0.4%vs MA</t>
-  </si>
-  <si>
     <t>Resistencia ▾</t>
   </si>
   <si>
-    <t>11.185 ▲ 38.1%vs MA</t>
-  </si>
-  <si>
-    <t>78 0.7% ▼ 40.5%vs MA</t>
-  </si>
-  <si>
-    <t>14 0.1% ▼ 17.6%vs MA</t>
-  </si>
-  <si>
-    <t>$235K ▼ 35.9%vs MA</t>
-  </si>
-  <si>
-    <t>98.7% ▲ 0.9%vs MA</t>
-  </si>
-  <si>
     <t>3 de febrero ▾</t>
   </si>
   <si>
-    <t>5.152 ▼ 42.5%vs MA</t>
-  </si>
-  <si>
-    <t>66 1.3% ▼ 63.3%vs MA</t>
-  </si>
-  <si>
-    <t>7 0.1% ▼ 85.4%vs MA</t>
-  </si>
-  <si>
-    <t>$235K ▼ 45.8%vs MA</t>
-  </si>
-  <si>
-    <t>97.7% ▲ 0.6%vs MA</t>
-  </si>
-  <si>
     <t>Santiago del Estero Sur ▾</t>
   </si>
   <si>
-    <t>14.443 ▲ 5.8%vs MA</t>
-  </si>
-  <si>
-    <t>86 0.6% ▼ 23.2%vs MA</t>
-  </si>
-  <si>
-    <t>71 0.5% ▼ 51.0%vs MA</t>
-  </si>
-  <si>
-    <t>$159K ▼ 49.8%vs MA</t>
-  </si>
-  <si>
-    <t>99.1% ▲ 0.2%vs MA</t>
-  </si>
-  <si>
     <t>Córdoba Este ▾</t>
   </si>
   <si>
-    <t>9.195 ▼ 63.9%vs MA</t>
-  </si>
-  <si>
-    <t>46 0.5% ▼ 69.5%vs MA</t>
-  </si>
-  <si>
-    <t>72 0.8% ▼ 73.1%vs MA</t>
-  </si>
-  <si>
-    <t>$154K ▼ 67.5%vs MA</t>
-  </si>
-  <si>
-    <t>99.2% ▲ 0.3%vs MA</t>
-  </si>
-  <si>
     <t>San Martín Mendoza ▾</t>
   </si>
   <si>
-    <t>5.018 ▲ 93.0%vs MA</t>
-  </si>
-  <si>
-    <t>49 1.0% ▲ 69.0%vs MA</t>
-  </si>
-  <si>
-    <t>4 0.1% ▼ 66.7%vs MA</t>
-  </si>
-  <si>
-    <t>$146K ▲ 110.4%vs MA</t>
-  </si>
-  <si>
-    <t>98.8% ▲ 0.9%vs MA</t>
-  </si>
-  <si>
     <t>Bariloche ▾</t>
   </si>
   <si>
-    <t>1.588 ▼ 21.9%vs MA</t>
-  </si>
-  <si>
-    <t>53 3.3% ▼ 54.7%vs MA</t>
-  </si>
-  <si>
-    <t>1 0.1% ▼ 95.2%vs MA</t>
-  </si>
-  <si>
-    <t>$141K ▼ 64.7%vs MA</t>
-  </si>
-  <si>
-    <t>95.2% ▲ 3.0%vs MA</t>
-  </si>
-  <si>
     <t>Posadas ▾</t>
   </si>
   <si>
-    <t>4.023 ▲ 65.9%vs MA</t>
-  </si>
-  <si>
-    <t>71 1.8% ▲ 69.0%vs MA</t>
-  </si>
-  <si>
-    <t>13 0.3% ▲ 44.4%vs MA</t>
-  </si>
-  <si>
-    <t>$140K ▲ 28.3%vs MA</t>
-  </si>
-  <si>
-    <t>97.6% ▲ 0.3%vs MA</t>
-  </si>
-  <si>
     <t>Catamarca ▾</t>
   </si>
   <si>
-    <t>1.550 ▲ 75.9%vs MA</t>
-  </si>
-  <si>
-    <t>56 3.6% ▲ 229.4%vs MA</t>
-  </si>
-  <si>
     <t>0 0.0% ▼ 100.0%vs MA</t>
   </si>
   <si>
-    <t>$129K ▲ 94.2%vs MA</t>
-  </si>
-  <si>
-    <t>95.5% ▼ 0.1%vs MA</t>
-  </si>
-  <si>
     <t>Puerto Madryn ▾</t>
   </si>
   <si>
-    <t>2.331 ▲ 65.4%vs MA</t>
-  </si>
-  <si>
-    <t>36 1.5% ▲ 125.0%vs MA</t>
-  </si>
-  <si>
-    <t>9 0.4% ▼ 55.0%vs MA</t>
-  </si>
-  <si>
-    <t>$121K ▲ 123.1%vs MA</t>
-  </si>
-  <si>
-    <t>97.0% ▼ 0.4%vs MA</t>
-  </si>
-  <si>
     <t>La Rioja ▾</t>
   </si>
   <si>
-    <t>3.511 ▲ 77.3%vs MA</t>
-  </si>
-  <si>
-    <t>35 1.0% ▲ 25.0%vs MA</t>
-  </si>
-  <si>
-    <t>2 0.1%</t>
-  </si>
-  <si>
-    <t>$108K ▲ 63.2%vs MA</t>
-  </si>
-  <si>
-    <t>98.9% ▲ 0.6%vs MA</t>
-  </si>
-  <si>
     <t>Trelew ▾</t>
   </si>
   <si>
-    <t>1.788 ▲ 117.0%vs MA</t>
-  </si>
-  <si>
-    <t>28 1.6% ▼ 15.2%vs MA</t>
-  </si>
-  <si>
-    <t>1 0.1% ▲ 0.0%vs MA</t>
-  </si>
-  <si>
-    <t>$69K ▼ 42.1%vs MA</t>
-  </si>
-  <si>
-    <t>97.5% ▲ 3.9%vs MA</t>
-  </si>
-  <si>
     <t>Santiago ▾</t>
   </si>
   <si>
-    <t>2.992 ▲ 79.3%vs MA</t>
-  </si>
-  <si>
-    <t>16 0.5% ▼ 57.9%vs MA</t>
-  </si>
-  <si>
-    <t>5 0.2% ▲ 400.0%vs MA</t>
-  </si>
-  <si>
-    <t>$66K ▼ 50.3%vs MA</t>
-  </si>
-  <si>
-    <t>99.4% ▲ 1.8%vs MA</t>
-  </si>
-  <si>
     <t>General Roca ▾</t>
   </si>
   <si>
-    <t>3.327 ▼ 12.5%vs MA</t>
-  </si>
-  <si>
-    <t>24 0.7% ▼ 71.4%vs MA</t>
-  </si>
-  <si>
-    <t>16 0.5% ▼ 27.3%vs MA</t>
-  </si>
-  <si>
-    <t>$65K ▼ 64.4%vs MA</t>
-  </si>
-  <si>
-    <t>99.2% ▲ 2.2%vs MA</t>
-  </si>
-  <si>
     <t>Jujuy ▾</t>
   </si>
   <si>
-    <t>6.395 ▲ 24.9%vs MA</t>
-  </si>
-  <si>
-    <t>20 0.3% ▼ 89.2%vs MA</t>
-  </si>
-  <si>
-    <t>20 0.3% ▼ 77.3%vs MA</t>
-  </si>
-  <si>
-    <t>$64K ▼ 88.8%vs MA</t>
-  </si>
-  <si>
-    <t>99.3% ▲ 4.1%vs MA</t>
-  </si>
-  <si>
     <t>Villa Nueva ▾</t>
   </si>
   <si>
-    <t>1.927 ▲ 74.5%vs MA</t>
-  </si>
-  <si>
-    <t>26 1.3% ▼ 10.3%vs MA</t>
-  </si>
-  <si>
-    <t>2 0.1% ▲ 100.0%vs MA</t>
-  </si>
-  <si>
-    <t>$63K ▼ 31.9%vs MA</t>
-  </si>
-  <si>
-    <t>97.7% ▲ 1.6%vs MA</t>
-  </si>
-  <si>
     <t>Villa Mercedes ▾</t>
   </si>
   <si>
-    <t>8.397 ▲ 46.0%vs MA</t>
-  </si>
-  <si>
-    <t>22 0.3% ▲ 10.0%vs MA</t>
-  </si>
-  <si>
-    <t>74 0.9% ▲ 17.5%vs MA</t>
-  </si>
-  <si>
-    <t>$51K ▲ 130.0%vs MA</t>
-  </si>
-  <si>
-    <t>99.5% ▲ 0.1%vs MA</t>
-  </si>
-  <si>
     <t>La Pampa ▾</t>
   </si>
   <si>
-    <t>1.099 ▲ 59.3%vs MA</t>
-  </si>
-  <si>
-    <t>18 1.6% ▲ 157.1%vs MA</t>
-  </si>
-  <si>
-    <t>2 0.2% ▲ 0.0%vs MA</t>
-  </si>
-  <si>
-    <t>$46K ▲ 32.0%vs MA</t>
-  </si>
-  <si>
-    <t>97.2% ▼ 1.1%vs MA</t>
-  </si>
-  <si>
     <t>Junín ▾</t>
   </si>
   <si>
-    <t>2.806 ▲ 34.5%vs MA</t>
-  </si>
-  <si>
-    <t>12 0.4% ▼ 25.0%vs MA</t>
-  </si>
-  <si>
-    <t>$41K ▼ 37.0%vs MA</t>
-  </si>
-  <si>
     <t>Campana ▾</t>
   </si>
   <si>
-    <t>1.208 ▲ 120.8%vs MA</t>
-  </si>
-  <si>
-    <t>19 1.6% ▲ 280.0%vs MA</t>
-  </si>
-  <si>
     <t>0 0.0%</t>
   </si>
   <si>
-    <t>$35K ▲ 480.8%vs MA</t>
-  </si>
-  <si>
-    <t>98.4% ▲ 0.6%vs MA</t>
-  </si>
-  <si>
     <t>Gral. Pico ▾</t>
   </si>
   <si>
-    <t>1.777 ▲ 31.8%vs MA</t>
-  </si>
-  <si>
-    <t>16 0.9% ▲ 6.7%vs MA</t>
-  </si>
-  <si>
-    <t>17 1.0% ▲ 54.5%vs MA</t>
-  </si>
-  <si>
-    <t>$29K ▼ 28.6%vs MA</t>
-  </si>
-  <si>
-    <t>98.4% ▲ 1.3%vs MA</t>
-  </si>
-  <si>
     <t>Viedma ▾</t>
   </si>
   <si>
-    <t>531 ▼ 14.6%vs MA</t>
-  </si>
-  <si>
-    <t>14 2.6% ▲ 55.6%vs MA</t>
-  </si>
-  <si>
-    <t>9 1.7% ▲ 125.0%vs MA</t>
-  </si>
-  <si>
-    <t>$26K ▼ 42.5%vs MA</t>
-  </si>
-  <si>
-    <t>96.8% ▼ 1.6%vs MA</t>
-  </si>
-  <si>
     <t>Tucumán Concepción ▾</t>
   </si>
   <si>
-    <t>1.056 ▲ 377.8%vs MA</t>
-  </si>
-  <si>
-    <t>7 0.7% ▲ 16.7%vs MA</t>
-  </si>
-  <si>
-    <t>$24K ▲ 335.6%vs MA</t>
-  </si>
-  <si>
-    <t>99.3% ▲ 3.6%vs MA</t>
-  </si>
-  <si>
     <t>Oran ▾</t>
   </si>
   <si>
-    <t>362 ▼ 61.5%vs MA</t>
-  </si>
-  <si>
-    <t>6 1.7% ▲ 200.0%vs MA</t>
-  </si>
-  <si>
-    <t>$13K ▲ 71.2%vs MA</t>
-  </si>
-  <si>
-    <t>96.7% ▼ 2.6%vs MA</t>
-  </si>
-  <si>
     <t>San Pedro Jujuy ▾</t>
   </si>
   <si>
-    <t>80 ▼ 35.5%vs MA</t>
-  </si>
-  <si>
-    <t>7 8.8% ▲ 600.0%vs MA</t>
-  </si>
-  <si>
-    <t>$9K ▲ 313.6%vs MA</t>
-  </si>
-  <si>
-    <t>91.3% ▼ 8.0%vs MA</t>
-  </si>
-  <si>
     <t>Goya ▾</t>
   </si>
   <si>
-    <t>392 ▲ 41.0%vs MA</t>
-  </si>
-  <si>
-    <t>3 0.8% ▼ 40.0%vs MA</t>
-  </si>
-  <si>
-    <t>$8K ▲ 0.6%vs MA</t>
-  </si>
-  <si>
-    <t>99.0% ▲ 1.5%vs MA</t>
-  </si>
-  <si>
     <t>Tartagal ▾</t>
   </si>
   <si>
-    <t>669 ▲ 91.7%vs MA</t>
-  </si>
-  <si>
-    <t>24 3.6% ▲ 380.0%vs MA</t>
-  </si>
-  <si>
-    <t>$7K ▲ 7.0%vs MA</t>
-  </si>
-  <si>
-    <t>96.0% ▼ 0.3%vs MA</t>
-  </si>
-  <si>
     <t>Sáenz Peña. Chaco ▾</t>
   </si>
   <si>
-    <t>380 ▲ 2.4%vs MA</t>
-  </si>
-  <si>
-    <t>6 1.6% ▼ 45.5%vs MA</t>
-  </si>
-  <si>
-    <t>1 0.3%</t>
-  </si>
-  <si>
-    <t>$6K ▼ 73.4%vs MA</t>
-  </si>
-  <si>
-    <t>97.9% ▲ 2.9%vs MA</t>
-  </si>
-  <si>
     <t>San Vicente ▾</t>
   </si>
   <si>
-    <t>962 ▲ 157.2%vs MA</t>
-  </si>
-  <si>
-    <t>3 0.3% ▲ 0.0%vs MA</t>
-  </si>
-  <si>
-    <t>8 0.8%</t>
-  </si>
-  <si>
-    <t>$4K ▼ 18.2%vs MA</t>
-  </si>
-  <si>
-    <t>98.8% ▲ 0.1%vs MA</t>
-  </si>
-  <si>
     <t>Las Heras Mendoza ▾</t>
   </si>
   <si>
-    <t>7 ▼ 30.0%vs MA</t>
-  </si>
-  <si>
     <t>100.0% ▲ 0.0%vs MA</t>
   </si>
   <si>
     <t>Cordoba Sur ▾</t>
   </si>
   <si>
-    <t>9 ▼ 35.7%vs MA</t>
-  </si>
-  <si>
     <t>Tigre ▾</t>
   </si>
   <si>
@@ -951,33 +210,18 @@
     <t>Maipú ▾</t>
   </si>
   <si>
-    <t>15 ▲ 36.4%vs MA</t>
-  </si>
-  <si>
     <t>HC Avellaneda 2 ▾</t>
   </si>
   <si>
-    <t>2 ▼ 75.0%vs MA</t>
-  </si>
-  <si>
     <t>Tablada ▾</t>
   </si>
   <si>
-    <t>5 ▼ 50.0%vs MA</t>
-  </si>
-  <si>
     <t>Quilmes ▾</t>
   </si>
   <si>
-    <t>1.112 ▲ 27700.0%vs MA</t>
-  </si>
-  <si>
     <t>Neuquén 2 ▾</t>
   </si>
   <si>
-    <t>8 ▲ 300.0%vs MA</t>
-  </si>
-  <si>
     <t>Mataderos ▾</t>
   </si>
   <si>
@@ -996,9 +240,6 @@
     <t>Moreno ▾</t>
   </si>
   <si>
-    <t>4 ▼ 63.6%vs MA</t>
-  </si>
-  <si>
     <t>José C Paz ▾</t>
   </si>
   <si>
@@ -1014,18 +255,9 @@
     <t>Río Salí ▾</t>
   </si>
   <si>
-    <t>827 ▲ 30.6%vs MA</t>
-  </si>
-  <si>
-    <t>6 0.7%</t>
-  </si>
-  <si>
     <t>$0 ▼ 100.0%vs MA</t>
   </si>
   <si>
-    <t>100.0% ▲ 2.1%vs MA</t>
-  </si>
-  <si>
     <t>Moreno Shopping ▾</t>
   </si>
   <si>
@@ -1035,15 +267,9 @@
     <t>Paraná 2 ▾</t>
   </si>
   <si>
-    <t>8 ▼ 27.3%vs MA</t>
-  </si>
-  <si>
     <t>Laferrere ▾</t>
   </si>
   <si>
-    <t>2 ▼ 71.4%vs MA</t>
-  </si>
-  <si>
     <t>Hurlingham Villegas ▾</t>
   </si>
   <si>
@@ -1053,78 +279,42 @@
     <t>Hurlingham Vergara ▾</t>
   </si>
   <si>
-    <t>4 ▲ 300.0%vs MA</t>
-  </si>
-  <si>
     <t>Pergamino ▾</t>
   </si>
   <si>
-    <t>372 ▲ 75.5%vs MA</t>
-  </si>
-  <si>
-    <t>100.0% ▲ 0.5%vs MA</t>
-  </si>
-  <si>
     <t>Lanús ▾</t>
   </si>
   <si>
     <t>González Catán ▾</t>
   </si>
   <si>
-    <t>4 ▲ 100.0%vs MA</t>
-  </si>
-  <si>
     <t>Fuerza Aérea Cba. ▾</t>
   </si>
   <si>
-    <t>4 ▼ 55.6%vs MA</t>
-  </si>
-  <si>
     <t>Mendoza Benegas ▾</t>
   </si>
   <si>
-    <t>1 ▼ 85.7%vs MA</t>
-  </si>
-  <si>
     <t>Fuerza Aérea Salta ▾</t>
   </si>
   <si>
-    <t>8 ▼ 20.0%vs MA</t>
-  </si>
-  <si>
     <t>Lomas de Zamora ▾</t>
   </si>
   <si>
-    <t>8 ▼ 61.9%vs MA</t>
-  </si>
-  <si>
     <t>Rawson San Juan ▾</t>
   </si>
   <si>
-    <t>2 ▼ 50.0%vs MA</t>
-  </si>
-  <si>
     <t>Tucumán Av. Jujuy ▾</t>
   </si>
   <si>
-    <t>5 ▼ 58.3%vs MA</t>
-  </si>
-  <si>
     <t>Corrientes Av. Maipú ▾</t>
   </si>
   <si>
-    <t>17 ▼ 48.5%vs MA</t>
-  </si>
-  <si>
     <t>Formosa 2 ▾</t>
   </si>
   <si>
     <t>San Juan Norte ▾</t>
   </si>
   <si>
-    <t>11 ▼ 21.4%vs MA</t>
-  </si>
-  <si>
     <t>Comodoro 2 ▾</t>
   </si>
   <si>
@@ -1134,75 +324,33 @@
     <t>Caseros ▾</t>
   </si>
   <si>
-    <t>1 ▼ 80.0%vs MA</t>
-  </si>
-  <si>
     <t>Donato Álvarez ▾</t>
   </si>
   <si>
-    <t>8 ▲ 100.0%vs MA</t>
-  </si>
-  <si>
     <t>Posadas 2 ▾</t>
   </si>
   <si>
-    <t>6 ▼ 53.8%vs MA</t>
-  </si>
-  <si>
     <t>Santa Rosa ▾</t>
   </si>
   <si>
-    <t>6 ▲ 200.0%vs MA</t>
-  </si>
-  <si>
     <t>Tucuman Ejercito Nor. ▾</t>
   </si>
   <si>
-    <t>10 ▼ 41.2%vs MA</t>
-  </si>
-  <si>
     <t>Claypole ▾</t>
   </si>
   <si>
     <t>Clorinda ▾</t>
   </si>
   <si>
-    <t>283 ▲ 135.8%vs MA</t>
-  </si>
-  <si>
     <t>Morón ▾</t>
   </si>
   <si>
-    <t>2 ▲ 100.0%vs MA</t>
-  </si>
-  <si>
     <t>Moreno Derqui ▾</t>
   </si>
   <si>
-    <t>3 ▼ 62.5%vs MA</t>
-  </si>
-  <si>
     <t>Otros / Canales especiales ▾</t>
   </si>
   <si>
-    <t>1 33.3%</t>
-  </si>
-  <si>
-    <t>985.473 ▲ 24.8%vs MA</t>
-  </si>
-  <si>
-    <t>9.135 0.9% ▼ 18.9%vs MA</t>
-  </si>
-  <si>
-    <t>9.220 0.9% ▼ 9.5%vs MA</t>
-  </si>
-  <si>
-    <t>$29 M ▼ 23.9%vs MA</t>
-  </si>
-  <si>
-    <t>98.4% ▲ 0.8%vs MA</t>
-  </si>
-  <si>
     <t>Tiendas</t>
   </si>
   <si>
@@ -1219,6 +367,651 @@
   </si>
   <si>
     <t>Fill rate</t>
+  </si>
+  <si>
+    <t>29.678 ▼ 4.8%vs MA</t>
+  </si>
+  <si>
+    <t>330 1.1% ▼ 12.9%vs MA</t>
+  </si>
+  <si>
+    <t>378 1.3% ▼ 43.1%vs MA</t>
+  </si>
+  <si>
+    <t>$1 M ▼ 25.7%vs MA</t>
+  </si>
+  <si>
+    <t>97.9% ▲ 0.2%vs MA</t>
+  </si>
+  <si>
+    <t>17.701 ▼ 6.3%vs MA</t>
+  </si>
+  <si>
+    <t>298 1.7% ▼ 10.0%vs MA</t>
+  </si>
+  <si>
+    <t>400 2.3% ▼ 34.4%vs MA</t>
+  </si>
+  <si>
+    <t>$863K ▼ 48.6%vs MA</t>
+  </si>
+  <si>
+    <t>97.7% ▼ 0.1%vs MA</t>
+  </si>
+  <si>
+    <t>8.419 ▼ 17.8%vs MA</t>
+  </si>
+  <si>
+    <t>296 3.5% ▼ 33.8%vs MA</t>
+  </si>
+  <si>
+    <t>69 0.8% ▲ 72.5%vs MA</t>
+  </si>
+  <si>
+    <t>$848K ▼ 36.9%vs MA</t>
+  </si>
+  <si>
+    <t>95.2% ▲ 0.8%vs MA</t>
+  </si>
+  <si>
+    <t>23.508 ▲ 25.8%vs MA</t>
+  </si>
+  <si>
+    <t>120 0.5% ▲ 8.1%vs MA</t>
+  </si>
+  <si>
+    <t>438 1.9% ▲ 77.3%vs MA</t>
+  </si>
+  <si>
+    <t>$523K ▲ 125.5%vs MA</t>
+  </si>
+  <si>
+    <t>99.0% ▲ 0.3%vs MA</t>
+  </si>
+  <si>
+    <t>7.054 ▼ 5.1%vs MA</t>
+  </si>
+  <si>
+    <t>116 1.6% ▲ 146.8%vs MA</t>
+  </si>
+  <si>
+    <t>74 1.0% ▼ 24.5%vs MA</t>
+  </si>
+  <si>
+    <t>$432K ▲ 75.1%vs MA</t>
+  </si>
+  <si>
+    <t>97.7% ▼ 0.5%vs MA</t>
+  </si>
+  <si>
+    <t>8.817 ▲ 38.1%vs MA</t>
+  </si>
+  <si>
+    <t>140 1.6% ▲ 47.4%vs MA</t>
+  </si>
+  <si>
+    <t>65 0.7% ▲ 150.0%vs MA</t>
+  </si>
+  <si>
+    <t>$391K ▲ 38.7%vs MA</t>
+  </si>
+  <si>
+    <t>97.0% ▲ 0.0%vs MA</t>
+  </si>
+  <si>
+    <t>6.016 ▼ 24.1%vs MA</t>
+  </si>
+  <si>
+    <t>154 2.6% ▼ 41.4%vs MA</t>
+  </si>
+  <si>
+    <t>$383K ▼ 42.4%vs MA</t>
+  </si>
+  <si>
+    <t>96.6% ▲ 0.5%vs MA</t>
+  </si>
+  <si>
+    <t>7.929 ▼ 13.9%vs MA</t>
+  </si>
+  <si>
+    <t>112 1.4% ▲ 107.4%vs MA</t>
+  </si>
+  <si>
+    <t>20 0.3% ▲ 11.1%vs MA</t>
+  </si>
+  <si>
+    <t>$360K ▲ 56.4%vs MA</t>
+  </si>
+  <si>
+    <t>98.1% ▼ 1.1%vs MA</t>
+  </si>
+  <si>
+    <t>2.171 ▼ 35.9%vs MA</t>
+  </si>
+  <si>
+    <t>112 5.2% ▼ 39.8%vs MA</t>
+  </si>
+  <si>
+    <t>21 1.0% ▲ 0.0%vs MA</t>
+  </si>
+  <si>
+    <t>$298K ▼ 53.3%vs MA</t>
+  </si>
+  <si>
+    <t>93.8% ▲ 0.0%vs MA</t>
+  </si>
+  <si>
+    <t>11.728 ▼ 13.1%vs MA</t>
+  </si>
+  <si>
+    <t>134 1.1% ▲ 28.8%vs MA</t>
+  </si>
+  <si>
+    <t>165 1.4% ▼ 24.7%vs MA</t>
+  </si>
+  <si>
+    <t>$256K ▼ 47.2%vs MA</t>
+  </si>
+  <si>
+    <t>98.4% ▼ 0.4%vs MA</t>
+  </si>
+  <si>
+    <t>9.786 ▼ 18.0%vs MA</t>
+  </si>
+  <si>
+    <t>34 0.3% ▲ 36.0%vs MA</t>
+  </si>
+  <si>
+    <t>42 0.4% ▲ 16.7%vs MA</t>
+  </si>
+  <si>
+    <t>$202K ▲ 48.0%vs MA</t>
+  </si>
+  <si>
+    <t>98.9% ▼ 0.2%vs MA</t>
+  </si>
+  <si>
+    <t>18.135 ▼ 1.8%vs MA</t>
+  </si>
+  <si>
+    <t>52 0.3% ▼ 40.9%vs MA</t>
+  </si>
+  <si>
+    <t>140 0.8% ▲ 0.0%vs MA</t>
+  </si>
+  <si>
+    <t>$190K ▼ 36.0%vs MA</t>
+  </si>
+  <si>
+    <t>99.1% ▲ 0.5%vs MA</t>
+  </si>
+  <si>
+    <t>17.053 ▼ 24.0%vs MA</t>
+  </si>
+  <si>
+    <t>57 0.3% ▼ 59.3%vs MA</t>
+  </si>
+  <si>
+    <t>144 0.8% ▼ 42.2%vs MA</t>
+  </si>
+  <si>
+    <t>$157K ▼ 71.3%vs MA</t>
+  </si>
+  <si>
+    <t>99.2% ▲ 0.4%vs MA</t>
+  </si>
+  <si>
+    <t>4.930 ▼ 7.7%vs MA</t>
+  </si>
+  <si>
+    <t>47 1.0% ▲ 14.6%vs MA</t>
+  </si>
+  <si>
+    <t>55 1.1% ▼ 27.6%vs MA</t>
+  </si>
+  <si>
+    <t>$142K ▲ 31.5%vs MA</t>
+  </si>
+  <si>
+    <t>98.8% ▼ 0.1%vs MA</t>
+  </si>
+  <si>
+    <t>5.590 ▲ 3.3%vs MA</t>
+  </si>
+  <si>
+    <t>32 0.6% ▼ 61.4%vs MA</t>
+  </si>
+  <si>
+    <t>88 1.6% ▼ 24.8%vs MA</t>
+  </si>
+  <si>
+    <t>$139K ▼ 56.9%vs MA</t>
+  </si>
+  <si>
+    <t>98.7% ▲ 1.4%vs MA</t>
+  </si>
+  <si>
+    <t>6.199 ▼ 46.1%vs MA</t>
+  </si>
+  <si>
+    <t>50 0.8% ▼ 52.8%vs MA</t>
+  </si>
+  <si>
+    <t>41 0.7% ▼ 76.4%vs MA</t>
+  </si>
+  <si>
+    <t>$118K ▼ 60.1%vs MA</t>
+  </si>
+  <si>
+    <t>98.3% ▲ 0.0%vs MA</t>
+  </si>
+  <si>
+    <t>4.727 ▼ 46.8%vs MA</t>
+  </si>
+  <si>
+    <t>14 0.3% ▼ 86.5%vs MA</t>
+  </si>
+  <si>
+    <t>83 1.8% ▼ 39.4%vs MA</t>
+  </si>
+  <si>
+    <t>$107K ▼ 54.2%vs MA</t>
+  </si>
+  <si>
+    <t>99.3% ▲ 0.6%vs MA</t>
+  </si>
+  <si>
+    <t>4.500 ▼ 10.9%vs MA</t>
+  </si>
+  <si>
+    <t>44 1.0% ▼ 17.0%vs MA</t>
+  </si>
+  <si>
+    <t>6 0.1% ▲ 100.0%vs MA</t>
+  </si>
+  <si>
+    <t>$96K ▼ 32.5%vs MA</t>
+  </si>
+  <si>
+    <t>98.9% ▲ 0.2%vs MA</t>
+  </si>
+  <si>
+    <t>1.406 ▼ 25.7%vs MA</t>
+  </si>
+  <si>
+    <t>15 1.1% ▼ 34.8%vs MA</t>
+  </si>
+  <si>
+    <t>$46K ▲ 10.9%vs MA</t>
+  </si>
+  <si>
+    <t>614 ▲ 84.4%vs MA</t>
+  </si>
+  <si>
+    <t>13 2.1% ▲ 8.3%vs MA</t>
+  </si>
+  <si>
+    <t>$45K ▲ 16.2%vs MA</t>
+  </si>
+  <si>
+    <t>96.7% ▲ 1.6%vs MA</t>
+  </si>
+  <si>
+    <t>3.394 ▼ 26.3%vs MA</t>
+  </si>
+  <si>
+    <t>47 1.4% ▲ 88.0%vs MA</t>
+  </si>
+  <si>
+    <t>21 0.6% ▲ 61.5%vs MA</t>
+  </si>
+  <si>
+    <t>$44K ▼ 45.2%vs MA</t>
+  </si>
+  <si>
+    <t>98.4% ▼ 1.0%vs MA</t>
+  </si>
+  <si>
+    <t>4.799 ▲ 113.6%vs MA</t>
+  </si>
+  <si>
+    <t>17 0.4% ▼ 41.4%vs MA</t>
+  </si>
+  <si>
+    <t>1 0.0% ▼ 85.7%vs MA</t>
+  </si>
+  <si>
+    <t>$43K ▼ 62.2%vs MA</t>
+  </si>
+  <si>
+    <t>99.4% ▲ 1.7%vs MA</t>
+  </si>
+  <si>
+    <t>4.964 ▼ 27.1%vs MA</t>
+  </si>
+  <si>
+    <t>10 0.2% ▼ 64.3%vs MA</t>
+  </si>
+  <si>
+    <t>57 1.1% ▼ 44.7%vs MA</t>
+  </si>
+  <si>
+    <t>$40K ▼ 69.8%vs MA</t>
+  </si>
+  <si>
+    <t>99.5% ▲ 0.2%vs MA</t>
+  </si>
+  <si>
+    <t>273 ▼ 19.0%vs MA</t>
+  </si>
+  <si>
+    <t>8 2.9% ▲ 100.0%vs MA</t>
+  </si>
+  <si>
+    <t>1 0.4% ▼ 50.0%vs MA</t>
+  </si>
+  <si>
+    <t>$31K ▲ 164.0%vs MA</t>
+  </si>
+  <si>
+    <t>96.3% ▼ 1.3%vs MA</t>
+  </si>
+  <si>
+    <t>340 ▼ 43.3%vs MA</t>
+  </si>
+  <si>
+    <t>4 1.2% ▼ 71.4%vs MA</t>
+  </si>
+  <si>
+    <t>4 1.2%</t>
+  </si>
+  <si>
+    <t>$29K ▲ 55.0%vs MA</t>
+  </si>
+  <si>
+    <t>98.2% ▲ 0.9%vs MA</t>
+  </si>
+  <si>
+    <t>941 ▲ 12.6%vs MA</t>
+  </si>
+  <si>
+    <t>5 0.5% ▲ 66.7%vs MA</t>
+  </si>
+  <si>
+    <t>5 0.5% ▼ 37.5%vs MA</t>
+  </si>
+  <si>
+    <t>$29K ▲ 906.3%vs MA</t>
+  </si>
+  <si>
+    <t>99.5% ▼ 0.2%vs MA</t>
+  </si>
+  <si>
+    <t>608 ▼ 16.5%vs MA</t>
+  </si>
+  <si>
+    <t>9 1.5% ▼ 35.7%vs MA</t>
+  </si>
+  <si>
+    <t>$25K ▼ 31.0%vs MA</t>
+  </si>
+  <si>
+    <t>98.5% ▲ 0.7%vs MA</t>
+  </si>
+  <si>
+    <t>405 ▼ 38.7%vs MA</t>
+  </si>
+  <si>
+    <t>7 1.7% ▼ 63.2%vs MA</t>
+  </si>
+  <si>
+    <t>1 0.2% ▼ 50.0%vs MA</t>
+  </si>
+  <si>
+    <t>$22K ▼ 3.1%vs MA</t>
+  </si>
+  <si>
+    <t>98.0% ▲ 1.7%vs MA</t>
+  </si>
+  <si>
+    <t>1.831 ▼ 41.9%vs MA</t>
+  </si>
+  <si>
+    <t>9 0.5% ▼ 70.0%vs MA</t>
+  </si>
+  <si>
+    <t>4 0.2% ▼ 80.0%vs MA</t>
+  </si>
+  <si>
+    <t>$17K ▼ 76.8%vs MA</t>
+  </si>
+  <si>
+    <t>99.3% ▲ 0.8%vs MA</t>
+  </si>
+  <si>
+    <t>84 ▼ 85.2%vs MA</t>
+  </si>
+  <si>
+    <t>6 7.1% ▼ 80.6%vs MA</t>
+  </si>
+  <si>
+    <t>$15K ▼ 79.1%vs MA</t>
+  </si>
+  <si>
+    <t>92.9% ▼ 1.4%vs MA</t>
+  </si>
+  <si>
+    <t>396 ▼ 52.5%vs MA</t>
+  </si>
+  <si>
+    <t>6 1.5% ▼ 73.9%vs MA</t>
+  </si>
+  <si>
+    <t>$13K ▼ 75.7%vs MA</t>
+  </si>
+  <si>
+    <t>95.2% ▼ 1.2%vs MA</t>
+  </si>
+  <si>
+    <t>284 ▲ 69.0%vs MA</t>
+  </si>
+  <si>
+    <t>7 2.5%</t>
+  </si>
+  <si>
+    <t>1 0.4% ▼ 75.0%vs MA</t>
+  </si>
+  <si>
+    <t>$12K</t>
+  </si>
+  <si>
+    <t>97.5% ▼ 1.9%vs MA</t>
+  </si>
+  <si>
+    <t>481 ▼ 34.5%vs MA</t>
+  </si>
+  <si>
+    <t>3 0.6%</t>
+  </si>
+  <si>
+    <t>99.0% ▼ 0.9%vs MA</t>
+  </si>
+  <si>
+    <t>1.213 ▼ 57.9%vs MA</t>
+  </si>
+  <si>
+    <t>2 0.2% ▼ 89.5%vs MA</t>
+  </si>
+  <si>
+    <t>9 0.7% ▼ 71.0%vs MA</t>
+  </si>
+  <si>
+    <t>$9K ▼ 76.2%vs MA</t>
+  </si>
+  <si>
+    <t>99.8% ▲ 0.9%vs MA</t>
+  </si>
+  <si>
+    <t>436 ▼ 1.8%vs MA</t>
+  </si>
+  <si>
+    <t>3 0.7% ▼ 62.5%vs MA</t>
+  </si>
+  <si>
+    <t>2 0.5% ▼ 33.3%vs MA</t>
+  </si>
+  <si>
+    <t>$7K ▲ 3.4%vs MA</t>
+  </si>
+  <si>
+    <t>95.9% ▼ 2.1%vs MA</t>
+  </si>
+  <si>
+    <t>212 ▼ 46.1%vs MA</t>
+  </si>
+  <si>
+    <t>1 0.5% ▼ 92.3%vs MA</t>
+  </si>
+  <si>
+    <t>4 1.9%</t>
+  </si>
+  <si>
+    <t>$3K ▼ 88.3%vs MA</t>
+  </si>
+  <si>
+    <t>99.1% ▲ 2.7%vs MA</t>
+  </si>
+  <si>
+    <t>90 ▼ 65.8%vs MA</t>
+  </si>
+  <si>
+    <t>1 1.1% ▼ 50.0%vs MA</t>
+  </si>
+  <si>
+    <t>$2K ▼ 58.9%vs MA</t>
+  </si>
+  <si>
+    <t>98.9% ▲ 1.2%vs MA</t>
+  </si>
+  <si>
+    <t>2.750 ▼ 6.9%vs MA</t>
+  </si>
+  <si>
+    <t>2 0.1% ▼ 66.7%vs MA</t>
+  </si>
+  <si>
+    <t>3 0.1% ▼ 89.3%vs MA</t>
+  </si>
+  <si>
+    <t>$2K ▼ 88.6%vs MA</t>
+  </si>
+  <si>
+    <t>99.5% ▲ 0.3%vs MA</t>
+  </si>
+  <si>
+    <t>138 ▲ 19.0%vs MA</t>
+  </si>
+  <si>
+    <t>1 0.7% ▲ 0.0%vs MA</t>
+  </si>
+  <si>
+    <t>$2K ▼ 56.9%vs MA</t>
+  </si>
+  <si>
+    <t>99.3% ▲ 0.1%vs MA</t>
+  </si>
+  <si>
+    <t>545 ▼ 10.9%vs MA</t>
+  </si>
+  <si>
+    <t>1 0.2% ▼ 83.3%vs MA</t>
+  </si>
+  <si>
+    <t>$934 ▼ 95.4%vs MA</t>
+  </si>
+  <si>
+    <t>99.6% ▲ 1.1%vs MA</t>
+  </si>
+  <si>
+    <t>3 ▼ 99.9%vs MA</t>
+  </si>
+  <si>
+    <t>100.0% ▲ 3.9%vs MA</t>
+  </si>
+  <si>
+    <t>1.057 ▼ 3.3%vs MA</t>
+  </si>
+  <si>
+    <t>4 0.4% ▲ 0.0%vs MA</t>
+  </si>
+  <si>
+    <t>99.1% ▼ 0.6%vs MA</t>
+  </si>
+  <si>
+    <t>128 ▲ 54.2%vs MA</t>
+  </si>
+  <si>
+    <t>32 ▼ 81.7%vs MA</t>
+  </si>
+  <si>
+    <t>37 ▼ 35.1%vs MA</t>
+  </si>
+  <si>
+    <t>89.2% ▼ 9.2%vs MA</t>
+  </si>
+  <si>
+    <t>26 ▼ 89.4%vs MA</t>
+  </si>
+  <si>
+    <t>100.0% ▲ 6.5%vs MA</t>
+  </si>
+  <si>
+    <t>76 ▲ 94.9%vs MA</t>
+  </si>
+  <si>
+    <t>98.7% ▲ 6.9%vs MA</t>
+  </si>
+  <si>
+    <t>189 ▲ 25.2%vs MA</t>
+  </si>
+  <si>
+    <t>3 ▲ 200.0%vs MA</t>
+  </si>
+  <si>
+    <t>5 ▲ 25.0%vs MA</t>
+  </si>
+  <si>
+    <t>121 ▲ 98.4%vs MA</t>
+  </si>
+  <si>
+    <t>99.2% ▲ 0.8%vs MA</t>
+  </si>
+  <si>
+    <t>4 ▲ 33.3%vs MA</t>
+  </si>
+  <si>
+    <t>8 ▼ 69.2%vs MA</t>
+  </si>
+  <si>
+    <t>134 ▼ 23.0%vs MA</t>
+  </si>
+  <si>
+    <t>99.3% ▲ 0.4%vs MA</t>
+  </si>
+  <si>
+    <t>222.297 ▼ 16.2%vs MA</t>
+  </si>
+  <si>
+    <t>2.319 1.0% ▼ 26.8%vs MA</t>
+  </si>
+  <si>
+    <t>2.349 1.1% ▼ 26.8%vs MA</t>
+  </si>
+  <si>
+    <t>$7 M ▼ 34.9%vs MA</t>
+  </si>
+  <si>
+    <t>98.3% ▲ 0.2%vs MA</t>
   </si>
 </sst>
 </file>
@@ -1555,1152 +1348,1152 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>392</v>
+        <v>108</v>
       </c>
       <c r="B1" t="s">
-        <v>393</v>
+        <v>109</v>
       </c>
       <c r="C1" t="s">
-        <v>394</v>
+        <v>110</v>
       </c>
       <c r="D1" t="s">
-        <v>395</v>
+        <v>111</v>
       </c>
       <c r="E1" t="s">
-        <v>396</v>
+        <v>112</v>
       </c>
       <c r="F1" t="s">
-        <v>397</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>114</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>3</v>
+        <v>115</v>
       </c>
       <c r="D2" t="s">
-        <v>4</v>
+        <v>116</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>117</v>
       </c>
       <c r="F2" t="s">
-        <v>6</v>
+        <v>118</v>
       </c>
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>119</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>120</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>121</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>122</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>123</v>
       </c>
       <c r="H3" s="2"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>15</v>
+        <v>125</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>126</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="F4" t="s">
-        <v>18</v>
+        <v>128</v>
       </c>
       <c r="H4" s="2"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>129</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>131</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>132</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>133</v>
       </c>
       <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>134</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>135</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>136</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>137</v>
       </c>
       <c r="F6" t="s">
-        <v>30</v>
+        <v>138</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>139</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>33</v>
+        <v>140</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>141</v>
       </c>
       <c r="E7" t="s">
-        <v>35</v>
+        <v>142</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>143</v>
       </c>
       <c r="H7" s="2"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>144</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E8" t="s">
-        <v>41</v>
+        <v>146</v>
       </c>
       <c r="F8" t="s">
-        <v>42</v>
+        <v>147</v>
       </c>
       <c r="H8" s="2"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>148</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>149</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>150</v>
       </c>
       <c r="E9" t="s">
-        <v>47</v>
+        <v>151</v>
       </c>
       <c r="F9" t="s">
-        <v>48</v>
+        <v>152</v>
       </c>
       <c r="H9" s="2"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>153</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>51</v>
+        <v>154</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>155</v>
       </c>
       <c r="E10" t="s">
-        <v>53</v>
+        <v>156</v>
       </c>
       <c r="F10" t="s">
-        <v>54</v>
+        <v>157</v>
       </c>
       <c r="H10" s="2"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>158</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>159</v>
       </c>
       <c r="D11" t="s">
-        <v>58</v>
+        <v>160</v>
       </c>
       <c r="E11" t="s">
-        <v>59</v>
+        <v>161</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>162</v>
       </c>
       <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>163</v>
       </c>
       <c r="C12" t="s">
-        <v>63</v>
+        <v>164</v>
       </c>
       <c r="D12" t="s">
-        <v>64</v>
+        <v>165</v>
       </c>
       <c r="E12" t="s">
-        <v>65</v>
+        <v>166</v>
       </c>
       <c r="F12" t="s">
-        <v>66</v>
+        <v>167</v>
       </c>
       <c r="H12" s="2"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>169</v>
       </c>
       <c r="D13" t="s">
-        <v>70</v>
+        <v>170</v>
       </c>
       <c r="E13" t="s">
-        <v>71</v>
+        <v>171</v>
       </c>
       <c r="F13" t="s">
-        <v>72</v>
+        <v>172</v>
       </c>
       <c r="H13" s="2"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>73</v>
+        <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>173</v>
       </c>
       <c r="C14" t="s">
-        <v>75</v>
+        <v>174</v>
       </c>
       <c r="D14" t="s">
-        <v>76</v>
+        <v>175</v>
       </c>
       <c r="E14" t="s">
-        <v>77</v>
+        <v>176</v>
       </c>
       <c r="F14" t="s">
-        <v>78</v>
+        <v>177</v>
       </c>
       <c r="H14" s="2"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>178</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>179</v>
       </c>
       <c r="D15" t="s">
-        <v>82</v>
+        <v>180</v>
       </c>
       <c r="E15" t="s">
-        <v>83</v>
+        <v>181</v>
       </c>
       <c r="F15" t="s">
-        <v>84</v>
+        <v>182</v>
       </c>
       <c r="H15" s="2"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>86</v>
+        <v>183</v>
       </c>
       <c r="C16" t="s">
-        <v>87</v>
+        <v>184</v>
       </c>
       <c r="D16" t="s">
-        <v>88</v>
+        <v>185</v>
       </c>
       <c r="E16" t="s">
-        <v>89</v>
+        <v>186</v>
       </c>
       <c r="F16" t="s">
-        <v>90</v>
+        <v>187</v>
       </c>
       <c r="H16" s="2"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>188</v>
       </c>
       <c r="C17" t="s">
-        <v>93</v>
+        <v>189</v>
       </c>
       <c r="D17" t="s">
-        <v>94</v>
+        <v>190</v>
       </c>
       <c r="E17" t="s">
-        <v>95</v>
+        <v>191</v>
       </c>
       <c r="F17" t="s">
-        <v>96</v>
+        <v>192</v>
       </c>
       <c r="H17" s="2"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>97</v>
+        <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>98</v>
+        <v>193</v>
       </c>
       <c r="C18" t="s">
-        <v>99</v>
+        <v>194</v>
       </c>
       <c r="D18" t="s">
-        <v>100</v>
+        <v>195</v>
       </c>
       <c r="E18" t="s">
-        <v>101</v>
+        <v>196</v>
       </c>
       <c r="F18" t="s">
-        <v>102</v>
+        <v>197</v>
       </c>
       <c r="H18" s="2"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>103</v>
+        <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>104</v>
+        <v>198</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>105</v>
+        <v>199</v>
       </c>
       <c r="D19" t="s">
-        <v>106</v>
+        <v>200</v>
       </c>
       <c r="E19" t="s">
-        <v>107</v>
+        <v>201</v>
       </c>
       <c r="F19" t="s">
-        <v>108</v>
+        <v>202</v>
       </c>
       <c r="H19" s="2"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>110</v>
+        <v>203</v>
       </c>
       <c r="C20" t="s">
-        <v>111</v>
+        <v>204</v>
       </c>
       <c r="D20" t="s">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="E20" t="s">
-        <v>113</v>
+        <v>205</v>
       </c>
       <c r="F20" t="s">
-        <v>114</v>
+        <v>23</v>
       </c>
       <c r="H20" s="2"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>115</v>
+        <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>116</v>
+        <v>206</v>
       </c>
       <c r="C21" t="s">
-        <v>117</v>
+        <v>207</v>
       </c>
       <c r="D21" t="s">
-        <v>118</v>
+        <v>33</v>
       </c>
       <c r="E21" t="s">
-        <v>119</v>
+        <v>208</v>
       </c>
       <c r="F21" t="s">
-        <v>120</v>
+        <v>209</v>
       </c>
       <c r="H21" s="2"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>121</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>122</v>
+        <v>210</v>
       </c>
       <c r="C22" t="s">
-        <v>123</v>
+        <v>211</v>
       </c>
       <c r="D22" t="s">
-        <v>124</v>
+        <v>212</v>
       </c>
       <c r="E22" t="s">
-        <v>125</v>
+        <v>213</v>
       </c>
       <c r="F22" t="s">
-        <v>126</v>
+        <v>214</v>
       </c>
       <c r="H22" s="2"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>127</v>
+        <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>128</v>
+        <v>215</v>
       </c>
       <c r="C23" t="s">
-        <v>129</v>
+        <v>216</v>
       </c>
       <c r="D23" t="s">
-        <v>130</v>
+        <v>217</v>
       </c>
       <c r="E23" t="s">
-        <v>131</v>
+        <v>218</v>
       </c>
       <c r="F23" t="s">
-        <v>132</v>
+        <v>219</v>
       </c>
       <c r="H23" s="2"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>133</v>
+        <v>15</v>
       </c>
       <c r="B24" t="s">
-        <v>134</v>
+        <v>220</v>
       </c>
       <c r="C24" t="s">
-        <v>135</v>
+        <v>221</v>
       </c>
       <c r="D24" t="s">
-        <v>136</v>
+        <v>222</v>
       </c>
       <c r="E24" t="s">
-        <v>137</v>
+        <v>223</v>
       </c>
       <c r="F24" t="s">
-        <v>138</v>
+        <v>224</v>
       </c>
       <c r="H24" s="2"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>139</v>
+        <v>34</v>
       </c>
       <c r="B25" t="s">
-        <v>140</v>
+        <v>225</v>
       </c>
       <c r="C25" t="s">
-        <v>141</v>
+        <v>226</v>
       </c>
       <c r="D25" t="s">
-        <v>142</v>
+        <v>227</v>
       </c>
       <c r="E25" t="s">
-        <v>143</v>
+        <v>228</v>
       </c>
       <c r="F25" t="s">
-        <v>144</v>
+        <v>229</v>
       </c>
       <c r="H25" s="2"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>145</v>
+        <v>29</v>
       </c>
       <c r="B26" t="s">
-        <v>146</v>
+        <v>230</v>
       </c>
       <c r="C26" t="s">
-        <v>147</v>
+        <v>231</v>
       </c>
       <c r="D26" t="s">
-        <v>148</v>
+        <v>232</v>
       </c>
       <c r="E26" t="s">
-        <v>149</v>
+        <v>233</v>
       </c>
       <c r="F26" t="s">
-        <v>150</v>
+        <v>234</v>
       </c>
       <c r="H26" s="2"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>151</v>
+        <v>38</v>
       </c>
       <c r="B27" t="s">
-        <v>152</v>
+        <v>235</v>
       </c>
       <c r="C27" t="s">
-        <v>153</v>
+        <v>236</v>
       </c>
       <c r="D27" t="s">
-        <v>154</v>
+        <v>237</v>
       </c>
       <c r="E27" t="s">
-        <v>155</v>
+        <v>238</v>
       </c>
       <c r="F27" t="s">
-        <v>156</v>
+        <v>239</v>
       </c>
       <c r="H27" s="2"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>157</v>
+        <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>158</v>
+        <v>240</v>
       </c>
       <c r="C28" t="s">
-        <v>159</v>
+        <v>241</v>
       </c>
       <c r="D28" t="s">
-        <v>160</v>
+        <v>45</v>
       </c>
       <c r="E28" t="s">
-        <v>161</v>
+        <v>242</v>
       </c>
       <c r="F28" t="s">
-        <v>162</v>
+        <v>243</v>
       </c>
       <c r="H28" s="2"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>163</v>
+        <v>31</v>
       </c>
       <c r="B29" t="s">
-        <v>164</v>
+        <v>244</v>
       </c>
       <c r="C29" t="s">
-        <v>165</v>
+        <v>245</v>
       </c>
       <c r="D29" t="s">
-        <v>166</v>
+        <v>246</v>
       </c>
       <c r="E29" t="s">
-        <v>167</v>
+        <v>247</v>
       </c>
       <c r="F29" t="s">
-        <v>168</v>
+        <v>248</v>
       </c>
       <c r="H29" s="2"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>169</v>
+        <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>170</v>
+        <v>249</v>
       </c>
       <c r="C30" t="s">
-        <v>171</v>
+        <v>250</v>
       </c>
       <c r="D30" t="s">
-        <v>172</v>
+        <v>251</v>
       </c>
       <c r="E30" t="s">
-        <v>173</v>
+        <v>252</v>
       </c>
       <c r="F30" t="s">
-        <v>174</v>
+        <v>253</v>
       </c>
       <c r="H30" s="2"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>175</v>
+        <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>176</v>
+        <v>254</v>
       </c>
       <c r="C31" t="s">
-        <v>177</v>
+        <v>255</v>
       </c>
       <c r="D31" t="s">
-        <v>178</v>
+        <v>45</v>
       </c>
       <c r="E31" t="s">
-        <v>179</v>
+        <v>256</v>
       </c>
       <c r="F31" t="s">
-        <v>180</v>
+        <v>257</v>
       </c>
       <c r="H31" s="2"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>181</v>
+        <v>36</v>
       </c>
       <c r="B32" t="s">
-        <v>182</v>
+        <v>258</v>
       </c>
       <c r="C32" t="s">
-        <v>183</v>
+        <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>184</v>
+        <v>33</v>
       </c>
       <c r="E32" t="s">
-        <v>185</v>
+        <v>260</v>
       </c>
       <c r="F32" t="s">
-        <v>186</v>
+        <v>261</v>
       </c>
       <c r="H32" s="2"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>187</v>
+        <v>54</v>
       </c>
       <c r="B33" t="s">
-        <v>188</v>
+        <v>262</v>
       </c>
       <c r="C33" t="s">
-        <v>189</v>
+        <v>263</v>
       </c>
       <c r="D33" t="s">
-        <v>190</v>
+        <v>264</v>
       </c>
       <c r="E33" t="s">
-        <v>191</v>
+        <v>265</v>
       </c>
       <c r="F33" t="s">
-        <v>192</v>
+        <v>266</v>
       </c>
       <c r="H33" s="2"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>193</v>
+        <v>37</v>
       </c>
       <c r="B34" t="s">
-        <v>194</v>
+        <v>267</v>
       </c>
       <c r="C34" t="s">
-        <v>195</v>
+        <v>268</v>
       </c>
       <c r="D34" t="s">
-        <v>196</v>
+        <v>268</v>
       </c>
       <c r="E34" t="s">
-        <v>197</v>
+        <v>265</v>
       </c>
       <c r="F34" t="s">
-        <v>198</v>
+        <v>269</v>
       </c>
       <c r="H34" s="2"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>199</v>
+        <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>200</v>
+        <v>270</v>
       </c>
       <c r="C35" t="s">
-        <v>201</v>
+        <v>271</v>
       </c>
       <c r="D35" t="s">
-        <v>202</v>
+        <v>272</v>
       </c>
       <c r="E35" t="s">
-        <v>203</v>
+        <v>273</v>
       </c>
       <c r="F35" t="s">
-        <v>204</v>
+        <v>274</v>
       </c>
       <c r="H35" s="2"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>205</v>
+        <v>46</v>
       </c>
       <c r="B36" t="s">
-        <v>206</v>
+        <v>275</v>
       </c>
       <c r="C36" t="s">
-        <v>207</v>
+        <v>276</v>
       </c>
       <c r="D36" t="s">
-        <v>208</v>
+        <v>277</v>
       </c>
       <c r="E36" t="s">
-        <v>209</v>
+        <v>278</v>
       </c>
       <c r="F36" t="s">
-        <v>210</v>
+        <v>279</v>
       </c>
       <c r="H36" s="2"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>211</v>
+        <v>40</v>
       </c>
       <c r="B37" t="s">
-        <v>212</v>
+        <v>280</v>
       </c>
       <c r="C37" t="s">
-        <v>213</v>
+        <v>281</v>
       </c>
       <c r="D37" t="s">
-        <v>214</v>
+        <v>282</v>
       </c>
       <c r="E37" t="s">
-        <v>215</v>
+        <v>283</v>
       </c>
       <c r="F37" t="s">
-        <v>216</v>
+        <v>284</v>
       </c>
       <c r="H37" s="2"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>217</v>
+        <v>42</v>
       </c>
       <c r="B38" t="s">
-        <v>218</v>
+        <v>285</v>
       </c>
       <c r="C38" t="s">
-        <v>219</v>
+        <v>286</v>
       </c>
       <c r="D38" t="s">
-        <v>220</v>
+        <v>33</v>
       </c>
       <c r="E38" t="s">
-        <v>221</v>
+        <v>287</v>
       </c>
       <c r="F38" t="s">
-        <v>222</v>
+        <v>288</v>
       </c>
       <c r="H38" s="2"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>223</v>
+        <v>22</v>
       </c>
       <c r="B39" t="s">
-        <v>224</v>
+        <v>289</v>
       </c>
       <c r="C39" t="s">
-        <v>225</v>
+        <v>290</v>
       </c>
       <c r="D39" t="s">
-        <v>226</v>
+        <v>291</v>
       </c>
       <c r="E39" t="s">
-        <v>227</v>
+        <v>292</v>
       </c>
       <c r="F39" t="s">
-        <v>228</v>
+        <v>293</v>
       </c>
       <c r="H39" s="2"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>229</v>
+        <v>53</v>
       </c>
       <c r="B40" t="s">
-        <v>230</v>
+        <v>294</v>
       </c>
       <c r="C40" t="s">
-        <v>231</v>
+        <v>295</v>
       </c>
       <c r="D40" t="s">
-        <v>232</v>
+        <v>33</v>
       </c>
       <c r="E40" t="s">
-        <v>233</v>
+        <v>296</v>
       </c>
       <c r="F40" t="s">
-        <v>234</v>
+        <v>297</v>
       </c>
       <c r="H40" s="2"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>235</v>
+        <v>43</v>
       </c>
       <c r="B41" t="s">
-        <v>236</v>
+        <v>298</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>237</v>
+        <v>299</v>
       </c>
       <c r="D41" t="s">
-        <v>238</v>
+        <v>45</v>
       </c>
       <c r="E41" t="s">
-        <v>239</v>
+        <v>300</v>
       </c>
       <c r="F41" t="s">
-        <v>240</v>
+        <v>301</v>
       </c>
       <c r="H41" s="2"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>241</v>
+        <v>55</v>
       </c>
       <c r="B42" t="s">
-        <v>242</v>
+        <v>66</v>
       </c>
       <c r="C42" t="s">
-        <v>243</v>
+        <v>45</v>
       </c>
       <c r="D42" t="s">
-        <v>184</v>
-      </c>
-      <c r="E42" t="s">
-        <v>244</v>
+        <v>45</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
       </c>
       <c r="F42" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="H42" s="2"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>245</v>
+        <v>57</v>
       </c>
       <c r="B43" t="s">
-        <v>246</v>
+        <v>74</v>
       </c>
       <c r="C43" t="s">
-        <v>247</v>
+        <v>45</v>
       </c>
       <c r="D43" t="s">
-        <v>248</v>
-      </c>
-      <c r="E43" t="s">
-        <v>249</v>
+        <v>45</v>
+      </c>
+      <c r="E43" s="3">
+        <v>0</v>
       </c>
       <c r="F43" t="s">
-        <v>250</v>
+        <v>56</v>
       </c>
       <c r="H43" s="2"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>251</v>
-      </c>
-      <c r="B44" t="s">
-        <v>252</v>
+        <v>58</v>
+      </c>
+      <c r="B44">
+        <v>0</v>
       </c>
       <c r="C44" t="s">
-        <v>253</v>
+        <v>45</v>
       </c>
       <c r="D44" t="s">
-        <v>254</v>
-      </c>
-      <c r="E44" t="s">
-        <v>255</v>
+        <v>45</v>
+      </c>
+      <c r="E44" s="3">
+        <v>0</v>
       </c>
       <c r="F44" t="s">
-        <v>256</v>
+        <v>59</v>
       </c>
       <c r="H44" s="2"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>257</v>
+        <v>20</v>
       </c>
       <c r="B45" t="s">
-        <v>258</v>
+        <v>302</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>33</v>
       </c>
       <c r="D45" t="s">
-        <v>260</v>
+        <v>33</v>
       </c>
       <c r="E45" t="s">
-        <v>261</v>
+        <v>76</v>
       </c>
       <c r="F45" t="s">
-        <v>262</v>
+        <v>303</v>
       </c>
       <c r="H45" s="2"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>263</v>
+        <v>60</v>
       </c>
       <c r="B46" t="s">
-        <v>264</v>
+        <v>66</v>
       </c>
       <c r="C46" t="s">
-        <v>265</v>
+        <v>45</v>
       </c>
       <c r="D46" t="s">
-        <v>184</v>
-      </c>
-      <c r="E46" t="s">
-        <v>266</v>
+        <v>45</v>
+      </c>
+      <c r="E46" s="3">
+        <v>0</v>
       </c>
       <c r="F46" t="s">
-        <v>267</v>
+        <v>67</v>
       </c>
       <c r="H46" s="2"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>268</v>
-      </c>
-      <c r="B47" t="s">
-        <v>269</v>
+        <v>61</v>
+      </c>
+      <c r="B47">
+        <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>270</v>
+        <v>45</v>
       </c>
       <c r="D47" t="s">
-        <v>184</v>
-      </c>
-      <c r="E47" t="s">
-        <v>271</v>
+        <v>45</v>
+      </c>
+      <c r="E47" s="3">
+        <v>0</v>
       </c>
       <c r="F47" t="s">
-        <v>272</v>
+        <v>97</v>
       </c>
       <c r="H47" s="2"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>273</v>
+        <v>62</v>
       </c>
       <c r="B48" t="s">
-        <v>274</v>
+        <v>66</v>
       </c>
       <c r="C48" t="s">
-        <v>275</v>
+        <v>45</v>
       </c>
       <c r="D48" t="s">
-        <v>248</v>
-      </c>
-      <c r="E48" t="s">
-        <v>276</v>
+        <v>45</v>
+      </c>
+      <c r="E48" s="3">
+        <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>277</v>
+        <v>67</v>
       </c>
       <c r="H48" s="2"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>278</v>
-      </c>
-      <c r="B49" t="s">
-        <v>279</v>
+        <v>63</v>
+      </c>
+      <c r="B49">
+        <v>280</v>
       </c>
       <c r="C49" t="s">
-        <v>280</v>
+        <v>45</v>
       </c>
       <c r="D49" t="s">
-        <v>184</v>
-      </c>
-      <c r="E49" t="s">
-        <v>281</v>
+        <v>45</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
       </c>
       <c r="F49" t="s">
-        <v>282</v>
+        <v>97</v>
       </c>
       <c r="H49" s="2"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>283</v>
+        <v>64</v>
       </c>
       <c r="B50" t="s">
-        <v>284</v>
+        <v>82</v>
       </c>
       <c r="C50" t="s">
-        <v>285</v>
+        <v>45</v>
       </c>
       <c r="D50" t="s">
-        <v>248</v>
-      </c>
-      <c r="E50" t="s">
-        <v>286</v>
+        <v>45</v>
+      </c>
+      <c r="E50" s="3">
+        <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>287</v>
+        <v>56</v>
       </c>
       <c r="H50" s="2"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>288</v>
-      </c>
-      <c r="B51" t="s">
-        <v>289</v>
+        <v>65</v>
+      </c>
+      <c r="B51">
+        <v>4</v>
       </c>
       <c r="C51" t="s">
-        <v>290</v>
+        <v>45</v>
       </c>
       <c r="D51" t="s">
-        <v>291</v>
-      </c>
-      <c r="E51" t="s">
-        <v>292</v>
+        <v>45</v>
+      </c>
+      <c r="E51" s="3">
+        <v>0</v>
       </c>
       <c r="F51" t="s">
-        <v>293</v>
+        <v>97</v>
       </c>
       <c r="H51" s="2"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>294</v>
-      </c>
-      <c r="B52" t="s">
-        <v>295</v>
+        <v>68</v>
+      </c>
+      <c r="B52">
+        <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>296</v>
+        <v>45</v>
       </c>
       <c r="D52" t="s">
-        <v>297</v>
-      </c>
-      <c r="E52" t="s">
-        <v>298</v>
+        <v>45</v>
+      </c>
+      <c r="E52" s="3">
+        <v>0</v>
       </c>
       <c r="F52" t="s">
-        <v>299</v>
+        <v>97</v>
       </c>
       <c r="H52" s="2"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>300</v>
+        <v>70</v>
       </c>
       <c r="B53" t="s">
-        <v>301</v>
+        <v>66</v>
       </c>
       <c r="C53" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="D53" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="E53" s="3">
         <v>0</v>
       </c>
       <c r="F53" t="s">
-        <v>302</v>
+        <v>67</v>
       </c>
       <c r="H53" s="2"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>303</v>
-      </c>
-      <c r="B54" t="s">
-        <v>304</v>
+        <v>71</v>
+      </c>
+      <c r="B54">
+        <v>1</v>
       </c>
       <c r="C54" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="D54" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="E54" s="3">
         <v>0</v>
       </c>
       <c r="F54" t="s">
-        <v>302</v>
+        <v>97</v>
       </c>
       <c r="H54" s="2"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55" t="s">
+        <v>304</v>
+      </c>
+      <c r="C55" t="s">
+        <v>33</v>
+      </c>
+      <c r="D55" t="s">
         <v>305</v>
       </c>
-      <c r="B55">
-        <v>0</v>
-      </c>
-      <c r="C55" t="s">
-        <v>248</v>
-      </c>
-      <c r="D55" t="s">
-        <v>248</v>
-      </c>
-      <c r="E55" s="3">
-        <v>0</v>
+      <c r="E55" s="3" t="s">
+        <v>76</v>
       </c>
       <c r="F55" t="s">
         <v>306</v>
@@ -2709,839 +2502,839 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>307</v>
+        <v>73</v>
       </c>
       <c r="B56" t="s">
-        <v>308</v>
+        <v>72</v>
       </c>
       <c r="C56" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="D56" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="E56" s="3">
         <v>0</v>
       </c>
       <c r="F56" t="s">
-        <v>302</v>
+        <v>56</v>
       </c>
       <c r="H56" s="2"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>309</v>
+        <v>75</v>
       </c>
       <c r="B57" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C57" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="D57" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="E57" s="3">
         <v>0</v>
       </c>
       <c r="F57" t="s">
-        <v>302</v>
+        <v>56</v>
       </c>
       <c r="H57" s="2"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>311</v>
+        <v>26</v>
       </c>
       <c r="B58" t="s">
-        <v>312</v>
+        <v>66</v>
       </c>
       <c r="C58" t="s">
-        <v>248</v>
+        <v>33</v>
       </c>
       <c r="D58" t="s">
-        <v>248</v>
-      </c>
-      <c r="E58" s="3">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>76</v>
       </c>
       <c r="F58" t="s">
-        <v>302</v>
+        <v>67</v>
       </c>
       <c r="H58" s="2"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>313</v>
+        <v>77</v>
       </c>
       <c r="B59" t="s">
-        <v>314</v>
+        <v>66</v>
       </c>
       <c r="C59" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="D59" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="E59" s="3">
         <v>0</v>
       </c>
       <c r="F59" t="s">
-        <v>302</v>
+        <v>67</v>
       </c>
       <c r="H59" s="2"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>315</v>
-      </c>
-      <c r="B60" t="s">
-        <v>316</v>
+        <v>78</v>
+      </c>
+      <c r="B60">
+        <v>0</v>
       </c>
       <c r="C60" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="D60" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="E60" s="3">
         <v>0</v>
       </c>
       <c r="F60" t="s">
-        <v>302</v>
+        <v>59</v>
       </c>
       <c r="H60" s="2"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>317</v>
+        <v>79</v>
       </c>
       <c r="B61" t="s">
-        <v>318</v>
+        <v>69</v>
       </c>
       <c r="C61" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="D61" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
       </c>
       <c r="F61" t="s">
-        <v>319</v>
+        <v>56</v>
       </c>
       <c r="H61" s="2"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>320</v>
+        <v>80</v>
       </c>
       <c r="B62" t="s">
-        <v>321</v>
+        <v>66</v>
       </c>
       <c r="C62" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="D62" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="E62" s="3">
         <v>0</v>
       </c>
       <c r="F62" t="s">
-        <v>302</v>
+        <v>67</v>
       </c>
       <c r="H62" s="2"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>322</v>
-      </c>
-      <c r="B63" t="s">
-        <v>323</v>
+        <v>81</v>
+      </c>
+      <c r="B63">
+        <v>1</v>
       </c>
       <c r="C63" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="D63" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="E63" s="3">
         <v>0</v>
       </c>
       <c r="F63" t="s">
-        <v>302</v>
+        <v>97</v>
       </c>
       <c r="H63" s="2"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>324</v>
+        <v>83</v>
       </c>
       <c r="B64" t="s">
-        <v>325</v>
+        <v>66</v>
       </c>
       <c r="C64" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="D64" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="E64" s="3">
         <v>0</v>
       </c>
       <c r="F64" t="s">
-        <v>302</v>
+        <v>67</v>
       </c>
       <c r="H64" s="2"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>326</v>
+        <v>84</v>
       </c>
       <c r="B65" t="s">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="C65" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="D65" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="E65" s="3">
         <v>0</v>
       </c>
       <c r="F65" t="s">
-        <v>302</v>
+        <v>56</v>
       </c>
       <c r="H65" s="2"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>328</v>
-      </c>
-      <c r="B66" t="s">
-        <v>329</v>
+        <v>85</v>
+      </c>
+      <c r="B66">
+        <v>1</v>
       </c>
       <c r="C66" t="s">
-        <v>184</v>
+        <v>45</v>
       </c>
       <c r="D66" t="s">
-        <v>330</v>
-      </c>
-      <c r="E66" t="s">
-        <v>331</v>
+        <v>45</v>
+      </c>
+      <c r="E66" s="3">
+        <v>0</v>
       </c>
       <c r="F66" t="s">
-        <v>332</v>
+        <v>97</v>
       </c>
       <c r="H66" s="2"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>333</v>
+        <v>49</v>
       </c>
       <c r="B67" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="C67" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="D67" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="E67" s="3">
         <v>0</v>
       </c>
       <c r="F67" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="H67" s="2"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>334</v>
-      </c>
-      <c r="B68">
-        <v>0</v>
+        <v>47</v>
+      </c>
+      <c r="B68" t="s">
+        <v>311</v>
       </c>
       <c r="C68" t="s">
-        <v>248</v>
+        <v>33</v>
       </c>
       <c r="D68" t="s">
-        <v>248</v>
-      </c>
-      <c r="E68" s="3">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>76</v>
       </c>
       <c r="F68" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="H68" s="2"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>335</v>
+        <v>86</v>
       </c>
       <c r="B69" t="s">
-        <v>336</v>
+        <v>66</v>
       </c>
       <c r="C69" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="D69" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="E69" s="3">
         <v>0</v>
       </c>
       <c r="F69" t="s">
-        <v>302</v>
+        <v>67</v>
       </c>
       <c r="H69" s="2"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>337</v>
+        <v>87</v>
       </c>
       <c r="B70" t="s">
-        <v>338</v>
+        <v>82</v>
       </c>
       <c r="C70" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="D70" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="E70" s="3">
         <v>0</v>
       </c>
       <c r="F70" t="s">
-        <v>302</v>
+        <v>56</v>
       </c>
       <c r="H70" s="2"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>339</v>
-      </c>
-      <c r="B71" t="s">
-        <v>340</v>
+        <v>88</v>
+      </c>
+      <c r="B71">
+        <v>2</v>
       </c>
       <c r="C71" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="D71" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="E71" s="3">
         <v>0</v>
       </c>
       <c r="F71" t="s">
-        <v>302</v>
+        <v>97</v>
       </c>
       <c r="H71" s="2"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>341</v>
+        <v>51</v>
       </c>
       <c r="B72" t="s">
-        <v>342</v>
+        <v>313</v>
       </c>
       <c r="C72" t="s">
-        <v>248</v>
+        <v>33</v>
       </c>
       <c r="D72" t="s">
-        <v>248</v>
-      </c>
-      <c r="E72" s="3">
-        <v>0</v>
+        <v>45</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>76</v>
       </c>
       <c r="F72" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="H72" s="2"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>343</v>
-      </c>
-      <c r="B73" t="s">
-        <v>344</v>
+        <v>89</v>
+      </c>
+      <c r="B73">
+        <v>1</v>
       </c>
       <c r="C73" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="D73" t="s">
-        <v>184</v>
+        <v>45</v>
       </c>
       <c r="E73" s="3">
         <v>0</v>
       </c>
       <c r="F73" t="s">
-        <v>345</v>
+        <v>97</v>
       </c>
       <c r="H73" s="2"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>346</v>
+        <v>90</v>
       </c>
       <c r="B74" t="s">
-        <v>327</v>
+        <v>82</v>
       </c>
       <c r="C74" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="D74" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="E74" s="3">
         <v>0</v>
       </c>
       <c r="F74" t="s">
-        <v>302</v>
+        <v>56</v>
       </c>
       <c r="H74" s="2"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>347</v>
+        <v>52</v>
       </c>
       <c r="B75" t="s">
-        <v>348</v>
+        <v>315</v>
       </c>
       <c r="C75" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="D75" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="E75" s="3">
         <v>0</v>
       </c>
       <c r="F75" t="s">
-        <v>302</v>
+        <v>56</v>
       </c>
       <c r="H75" s="2"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>349</v>
+        <v>91</v>
       </c>
       <c r="B76" t="s">
-        <v>350</v>
+        <v>316</v>
       </c>
       <c r="C76" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="D76" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="E76" s="3">
         <v>0</v>
       </c>
       <c r="F76" t="s">
-        <v>302</v>
+        <v>56</v>
       </c>
       <c r="H76" s="2"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>351</v>
+        <v>92</v>
       </c>
       <c r="B77" t="s">
-        <v>352</v>
+        <v>82</v>
       </c>
       <c r="C77" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="D77" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="E77" s="3">
         <v>0</v>
       </c>
       <c r="F77" t="s">
-        <v>302</v>
+        <v>56</v>
       </c>
       <c r="H77" s="2"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>353</v>
+        <v>93</v>
       </c>
       <c r="B78" t="s">
-        <v>354</v>
+        <v>317</v>
       </c>
       <c r="C78" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="D78" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="E78" s="3">
         <v>0</v>
       </c>
       <c r="F78" t="s">
-        <v>302</v>
+        <v>56</v>
       </c>
       <c r="H78" s="2"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>355</v>
-      </c>
-      <c r="B79" t="s">
-        <v>356</v>
+        <v>94</v>
+      </c>
+      <c r="B79">
+        <v>0</v>
       </c>
       <c r="C79" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="D79" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="E79" s="3">
         <v>0</v>
       </c>
       <c r="F79" t="s">
-        <v>302</v>
+        <v>59</v>
       </c>
       <c r="H79" s="2"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>357</v>
+        <v>48</v>
       </c>
       <c r="B80" t="s">
-        <v>358</v>
+        <v>318</v>
       </c>
       <c r="C80" t="s">
-        <v>248</v>
+        <v>33</v>
       </c>
       <c r="D80" t="s">
-        <v>248</v>
-      </c>
-      <c r="E80" s="3">
-        <v>0</v>
+        <v>45</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>76</v>
       </c>
       <c r="F80" t="s">
-        <v>302</v>
+        <v>319</v>
       </c>
       <c r="H80" s="2"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>359</v>
-      </c>
-      <c r="B81" t="s">
-        <v>360</v>
+        <v>95</v>
+      </c>
+      <c r="B81">
+        <v>6</v>
       </c>
       <c r="C81" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="D81" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="E81" s="3">
         <v>0</v>
       </c>
       <c r="F81" t="s">
-        <v>302</v>
+        <v>97</v>
       </c>
       <c r="H81" s="2"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>361</v>
-      </c>
-      <c r="B82" t="s">
-        <v>362</v>
+        <v>96</v>
+      </c>
+      <c r="B82">
+        <v>1</v>
       </c>
       <c r="C82" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="D82" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="E82" s="3">
         <v>0</v>
       </c>
       <c r="F82" t="s">
-        <v>302</v>
+        <v>97</v>
       </c>
       <c r="H82" s="2"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>363</v>
-      </c>
-      <c r="B83">
-        <v>0</v>
+        <v>98</v>
+      </c>
+      <c r="B83" t="s">
+        <v>72</v>
       </c>
       <c r="C83" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="D83" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="E83" s="3">
         <v>0</v>
       </c>
       <c r="F83" t="s">
-        <v>306</v>
+        <v>56</v>
       </c>
       <c r="H83" s="2"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>364</v>
+        <v>99</v>
       </c>
       <c r="B84" t="s">
-        <v>365</v>
+        <v>66</v>
       </c>
       <c r="C84" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="D84" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="E84" s="3">
         <v>0</v>
       </c>
       <c r="F84" t="s">
-        <v>302</v>
+        <v>67</v>
       </c>
       <c r="H84" s="2"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>366</v>
-      </c>
-      <c r="B85">
-        <v>1</v>
+        <v>100</v>
+      </c>
+      <c r="B85" t="s">
+        <v>69</v>
       </c>
       <c r="C85" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="D85" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="E85" s="3">
         <v>0</v>
       </c>
       <c r="F85" t="s">
-        <v>367</v>
+        <v>56</v>
       </c>
       <c r="H85" s="2"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>368</v>
+        <v>101</v>
       </c>
       <c r="B86" t="s">
-        <v>369</v>
+        <v>66</v>
       </c>
       <c r="C86" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="D86" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="E86" s="3">
         <v>0</v>
       </c>
       <c r="F86" t="s">
-        <v>302</v>
+        <v>67</v>
       </c>
       <c r="H86" s="2"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>370</v>
-      </c>
-      <c r="B87" t="s">
-        <v>371</v>
+        <v>102</v>
+      </c>
+      <c r="B87">
+        <v>7</v>
       </c>
       <c r="C87" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="D87" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="E87" s="3">
         <v>0</v>
       </c>
       <c r="F87" t="s">
-        <v>302</v>
+        <v>97</v>
       </c>
       <c r="H87" s="2"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>372</v>
-      </c>
-      <c r="B88" t="s">
-        <v>373</v>
+        <v>103</v>
+      </c>
+      <c r="B88">
+        <v>0</v>
       </c>
       <c r="C88" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="D88" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="E88" s="3">
         <v>0</v>
       </c>
       <c r="F88" t="s">
-        <v>302</v>
+        <v>59</v>
       </c>
       <c r="H88" s="2"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>374</v>
+        <v>50</v>
       </c>
       <c r="B89" t="s">
-        <v>375</v>
+        <v>320</v>
       </c>
       <c r="C89" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="D89" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="E89" s="3">
         <v>0</v>
       </c>
       <c r="F89" t="s">
-        <v>302</v>
+        <v>56</v>
       </c>
       <c r="H89" s="2"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>376</v>
+        <v>104</v>
       </c>
       <c r="B90" t="s">
-        <v>377</v>
+        <v>321</v>
       </c>
       <c r="C90" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="D90" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="E90" s="3">
         <v>0</v>
       </c>
       <c r="F90" t="s">
-        <v>302</v>
+        <v>56</v>
       </c>
       <c r="H90" s="2"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>378</v>
+        <v>105</v>
       </c>
       <c r="B91" t="s">
-        <v>340</v>
+        <v>66</v>
       </c>
       <c r="C91" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="D91" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
       </c>
       <c r="F91" t="s">
-        <v>302</v>
+        <v>67</v>
       </c>
       <c r="H91" s="2"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>379</v>
-      </c>
-      <c r="B92" t="s">
-        <v>380</v>
+        <v>106</v>
+      </c>
+      <c r="B92">
+        <v>0</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="D92" t="s">
-        <v>248</v>
+        <v>45</v>
       </c>
       <c r="E92" s="3">
         <v>0</v>
       </c>
       <c r="F92" t="s">
-        <v>302</v>
+        <v>59</v>
       </c>
       <c r="H92" s="2"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>381</v>
+        <v>28</v>
       </c>
       <c r="B93" t="s">
-        <v>382</v>
+        <v>66</v>
       </c>
       <c r="C93" t="s">
-        <v>248</v>
+        <v>33</v>
       </c>
       <c r="D93" t="s">
-        <v>248</v>
-      </c>
-      <c r="E93" s="3">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>76</v>
       </c>
       <c r="F93" t="s">
-        <v>302</v>
+        <v>67</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>383</v>
+        <v>44</v>
       </c>
       <c r="B94" t="s">
-        <v>384</v>
+        <v>322</v>
       </c>
       <c r="C94" t="s">
-        <v>248</v>
+        <v>33</v>
       </c>
       <c r="D94" t="s">
-        <v>248</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
+        <v>45</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>76</v>
       </c>
       <c r="F94" t="s">
-        <v>302</v>
+        <v>323</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>385</v>
+        <v>107</v>
       </c>
       <c r="B95">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C95" t="s">
-        <v>184</v>
+        <v>45</v>
       </c>
       <c r="D95" t="s">
-        <v>386</v>
-      </c>
-      <c r="E95" t="s">
-        <v>331</v>
+        <v>45</v>
+      </c>
+      <c r="E95" s="3">
+        <v>0</v>
       </c>
       <c r="F95" t="s">
-        <v>367</v>
+        <v>97</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.35">
@@ -3549,19 +3342,19 @@
         <v>0</v>
       </c>
       <c r="B96" t="s">
-        <v>387</v>
+        <v>324</v>
       </c>
       <c r="C96" t="s">
-        <v>388</v>
+        <v>325</v>
       </c>
       <c r="D96" t="s">
-        <v>389</v>
+        <v>326</v>
       </c>
       <c r="E96" t="s">
-        <v>390</v>
+        <v>327</v>
       </c>
       <c r="F96" t="s">
-        <v>391</v>
+        <v>328</v>
       </c>
     </row>
   </sheetData>
